--- a/data/trans_orig/P1435_2011_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1435_2011_2023-Clase-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>432049</t>
+          <t>431774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292717</t>
+          <t>291730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308185</t>
+          <t>308082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>727145</t>
+          <t>728289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745191</t>
+          <t>744455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21737</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411232</t>
+          <t>411066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417869</t>
+          <t>417889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316151</t>
+          <t>316816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332082</t>
+          <t>331912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731400</t>
+          <t>730835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748643</t>
+          <t>748768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>25408</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>618938</t>
+          <t>619055</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>628359</t>
+          <t>628369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>249289</t>
+          <t>249365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>258202</t>
+          <t>258223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>872415</t>
+          <t>873228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>885411</t>
+          <t>885419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1153251</t>
+          <t>1154159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>720339</t>
+          <t>722380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>743439</t>
+          <t>745852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1878873</t>
+          <t>1879250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1903057</t>
+          <t>1903034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46794</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>503328</t>
+          <t>503525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>719849</t>
+          <t>720513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>740717</t>
+          <t>742169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1227206</t>
+          <t>1228326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250560</t>
+          <t>1251790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41009</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>43792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1060176</t>
+          <t>1059348</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1084913</t>
+          <t>1083664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1325408</t>
+          <t>1327026</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1350325</t>
+          <t>1351687</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49175</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50825</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3403640</t>
+          <t>3403063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3416010</t>
+          <t>3415960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3400169</t>
+          <t>3400158</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3446011</t>
+          <t>3445218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6807419</t>
+          <t>6808082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6855639</t>
+          <t>6856414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>104114</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>149956</t>
+          <t>149967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116396</t>
+          <t>115621</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>164616</t>
+          <t>163953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4265,32 +4265,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4300,32 +4300,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42640</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55692</t>
+          <t>59453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4335,32 +4335,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67370</t>
+          <t>71338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4378,32 +4378,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>495286</t>
+          <t>539914</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>487458</t>
+          <t>532824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500008</t>
+          <t>545274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4413,32 +4413,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>404666</t>
+          <t>441820</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>391614</t>
+          <t>428256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>414350</t>
+          <t>452632</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>899953</t>
+          <t>981734</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>885149</t>
+          <t>966989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>910733</t>
+          <t>993411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4491,17 +4491,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4526,17 +4526,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447306</t>
+          <t>487709</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447306</t>
+          <t>487709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447306</t>
+          <t>487709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952519</t>
+          <t>1038327</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952519</t>
+          <t>1038327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952519</t>
+          <t>1038327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4721,32 +4721,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4756,32 +4756,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33239</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24834</t>
+          <t>28305</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4791,32 +4791,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41856</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>59491</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -4834,32 +4834,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>443596</t>
+          <t>473572</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>436823</t>
+          <t>465695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>447824</t>
+          <t>478221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4869,32 +4869,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>347934</t>
+          <t>385116</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>337615</t>
+          <t>374148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>356339</t>
+          <t>393376</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4904,32 +4904,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>791530</t>
+          <t>858688</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>780131</t>
+          <t>845402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>801519</t>
+          <t>868668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -4947,17 +4947,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4982,17 +4982,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5017,17 +5017,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833386</t>
+          <t>904893</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833386</t>
+          <t>904893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833386</t>
+          <t>904893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5177,32 +5177,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5212,32 +5212,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10023</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5247,32 +5247,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32591</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5290,32 +5290,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>661513</t>
+          <t>464719</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653968</t>
+          <t>458344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665602</t>
+          <t>468041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5325,32 +5325,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>171124</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145774</t>
+          <t>163527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156888</t>
+          <t>176562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5360,32 +5360,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>813644</t>
+          <t>635844</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>800789</t>
+          <t>627034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>825781</t>
+          <t>642423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -5403,17 +5403,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5633,32 +5633,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5668,32 +5668,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>271334</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>62865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601838</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>286468</t>
+          <t>91994</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84996</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876719</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -5746,32 +5746,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1019685</t>
+          <t>1116153</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1010942</t>
+          <t>1107181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1025978</t>
+          <t>1121554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>706402</t>
+          <t>784529</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>375898</t>
+          <t>771340</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>898298</t>
+          <t>797968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1726087</t>
+          <t>1900682</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1135836</t>
+          <t>1884043</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1927559</t>
+          <t>1915846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977736</t>
+          <t>860833</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977736</t>
+          <t>860833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977736</t>
+          <t>860833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012555</t>
+          <t>1992676</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012555</t>
+          <t>1992676</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012555</t>
+          <t>1992676</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6089,32 +6089,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6124,32 +6124,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79564</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>59831</t>
+          <t>70037</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101502</t>
+          <t>98941</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6159,32 +6159,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>96080</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>81207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113864</t>
+          <t>114622</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6202,32 +6202,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>461752</t>
+          <t>553489</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>452531</t>
+          <t>543642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>467322</t>
+          <t>559385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6237,32 +6237,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>758801</t>
+          <t>746827</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>736863</t>
+          <t>730479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>778534</t>
+          <t>759383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6272,32 +6272,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1220553</t>
+          <t>1300316</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1198550</t>
+          <t>1281774</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1238698</t>
+          <t>1315189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -6315,17 +6315,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,17 +6350,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>838365</t>
+          <t>829420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1312414</t>
+          <t>1396396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6580,32 +6580,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>53412</t>
+          <t>61794</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>48954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66239</t>
+          <t>77973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6615,32 +6615,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>65184</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>50689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73295</t>
+          <t>82000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -6658,27 +6658,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>233838</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>221894</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6693,32 +6693,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>706633</t>
+          <t>781078</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>693806</t>
+          <t>764899</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>717194</t>
+          <t>793918</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6728,32 +6728,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>943318</t>
+          <t>1014916</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>927258</t>
+          <t>998100</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>955789</t>
+          <t>1029411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -6771,17 +6771,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760045</t>
+          <t>842872</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6841,17 +6841,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000553</t>
+          <t>1080100</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7001,32 +7001,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>44093</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7036,32 +7036,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>494971</t>
+          <t>319517</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>297723</t>
+          <t>292320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1169974</t>
+          <t>350914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7071,32 +7071,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>549722</t>
+          <t>377355</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>341317</t>
+          <t>343913</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1283709</t>
+          <t>411744</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7114,32 +7114,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3318518</t>
+          <t>3381684</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3299494</t>
+          <t>3363525</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3333043</t>
+          <t>3395429</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7149,32 +7149,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3076565</t>
+          <t>3310495</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2401562</t>
+          <t>3279098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3273813</t>
+          <t>3337692</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7184,32 +7184,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6395083</t>
+          <t>6692179</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5661096</t>
+          <t>6657790</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6603488</t>
+          <t>6725621</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -7227,17 +7227,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7262,17 +7262,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3571536</t>
+          <t>3630012</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3571536</t>
+          <t>3630012</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3571536</t>
+          <t>3630012</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7297,17 +7297,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6944805</t>
+          <t>7069534</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6944805</t>
+          <t>7069534</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6944805</t>
+          <t>7069534</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
